--- a/final_data_pipeline/output/311613longform.xlsx
+++ b/final_data_pipeline/output/311613longform.xlsx
@@ -3389,7 +3389,7 @@
         <v>109</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB30">
         <v>8000</v>
@@ -3478,7 +3478,7 @@
         <v>109</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB31">
         <v>8000</v>
@@ -3567,7 +3567,7 @@
         <v>109</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB32">
         <v>8000</v>
@@ -3656,7 +3656,7 @@
         <v>109</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB33">
         <v>8000</v>
@@ -3745,7 +3745,7 @@
         <v>109</v>
       </c>
       <c r="AA34">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB34">
         <v>8000</v>
@@ -3834,7 +3834,7 @@
         <v>109</v>
       </c>
       <c r="AA35">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB35">
         <v>8000</v>
@@ -3923,7 +3923,7 @@
         <v>109</v>
       </c>
       <c r="AA36">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB36">
         <v>8000</v>
@@ -4012,7 +4012,7 @@
         <v>109</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB37">
         <v>8000</v>
@@ -4101,7 +4101,7 @@
         <v>109</v>
       </c>
       <c r="AA38">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AB38">
         <v>8000</v>
@@ -4190,7 +4190,7 @@
         <v>109</v>
       </c>
       <c r="AA39">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AB39">
         <v>8000</v>
@@ -4279,7 +4279,7 @@
         <v>109</v>
       </c>
       <c r="AA40">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AB40">
         <v>8000</v>
@@ -4368,7 +4368,7 @@
         <v>109</v>
       </c>
       <c r="AA41">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AB41">
         <v>8000</v>
@@ -4457,7 +4457,7 @@
         <v>109</v>
       </c>
       <c r="AA42">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB42">
         <v>8000</v>
@@ -4546,7 +4546,7 @@
         <v>109</v>
       </c>
       <c r="AA43">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB43">
         <v>8000</v>
@@ -4635,7 +4635,7 @@
         <v>109</v>
       </c>
       <c r="AA44">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB44">
         <v>8000</v>
@@ -4724,7 +4724,7 @@
         <v>109</v>
       </c>
       <c r="AA45">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB45">
         <v>8000</v>
@@ -4813,7 +4813,7 @@
         <v>109</v>
       </c>
       <c r="AA46">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB46">
         <v>8000</v>
@@ -4902,7 +4902,7 @@
         <v>109</v>
       </c>
       <c r="AA47">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB47">
         <v>8000</v>
@@ -4991,7 +4991,7 @@
         <v>109</v>
       </c>
       <c r="AA48">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB48">
         <v>8000</v>
@@ -5080,7 +5080,7 @@
         <v>109</v>
       </c>
       <c r="AA49">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB49">
         <v>8000</v>
@@ -5169,7 +5169,7 @@
         <v>109</v>
       </c>
       <c r="AA50">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB50">
         <v>8000</v>
@@ -5258,7 +5258,7 @@
         <v>109</v>
       </c>
       <c r="AA51">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB51">
         <v>8000</v>
@@ -5347,7 +5347,7 @@
         <v>109</v>
       </c>
       <c r="AA52">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB52">
         <v>8000</v>
@@ -5436,7 +5436,7 @@
         <v>109</v>
       </c>
       <c r="AA53">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB53">
         <v>8000</v>
@@ -5525,7 +5525,7 @@
         <v>109</v>
       </c>
       <c r="AA54">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB54">
         <v>8000</v>
@@ -5614,7 +5614,7 @@
         <v>109</v>
       </c>
       <c r="AA55">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB55">
         <v>8000</v>
@@ -5703,7 +5703,7 @@
         <v>109</v>
       </c>
       <c r="AA56">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB56">
         <v>8000</v>
@@ -5792,7 +5792,7 @@
         <v>109</v>
       </c>
       <c r="AA57">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB57">
         <v>8000</v>
@@ -5881,7 +5881,7 @@
         <v>109</v>
       </c>
       <c r="AA58">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AB58">
         <v>8000</v>
@@ -5970,7 +5970,7 @@
         <v>109</v>
       </c>
       <c r="AA59">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AB59">
         <v>8000</v>
@@ -6059,7 +6059,7 @@
         <v>109</v>
       </c>
       <c r="AA60">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AB60">
         <v>8000</v>
@@ -6148,7 +6148,7 @@
         <v>109</v>
       </c>
       <c r="AA61">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AB61">
         <v>8000</v>
@@ -8729,7 +8729,7 @@
         <v>109</v>
       </c>
       <c r="AA90">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB90">
         <v>8000</v>
@@ -8818,7 +8818,7 @@
         <v>109</v>
       </c>
       <c r="AA91">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB91">
         <v>8000</v>
@@ -8907,7 +8907,7 @@
         <v>109</v>
       </c>
       <c r="AA92">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB92">
         <v>8000</v>
@@ -8996,7 +8996,7 @@
         <v>109</v>
       </c>
       <c r="AA93">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB93">
         <v>8000</v>
@@ -9085,7 +9085,7 @@
         <v>109</v>
       </c>
       <c r="AA94">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB94">
         <v>8000</v>
@@ -9174,7 +9174,7 @@
         <v>109</v>
       </c>
       <c r="AA95">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB95">
         <v>8000</v>
@@ -9263,7 +9263,7 @@
         <v>109</v>
       </c>
       <c r="AA96">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB96">
         <v>8000</v>
@@ -9352,7 +9352,7 @@
         <v>109</v>
       </c>
       <c r="AA97">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB97">
         <v>8000</v>
@@ -9441,7 +9441,7 @@
         <v>109</v>
       </c>
       <c r="AA98">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB98">
         <v>8000</v>
@@ -9530,7 +9530,7 @@
         <v>109</v>
       </c>
       <c r="AA99">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB99">
         <v>8000</v>
@@ -9619,7 +9619,7 @@
         <v>109</v>
       </c>
       <c r="AA100">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB100">
         <v>8000</v>
@@ -9708,7 +9708,7 @@
         <v>109</v>
       </c>
       <c r="AA101">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB101">
         <v>8000</v>
@@ -9797,7 +9797,7 @@
         <v>109</v>
       </c>
       <c r="AA102">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB102">
         <v>8000</v>
@@ -9886,7 +9886,7 @@
         <v>109</v>
       </c>
       <c r="AA103">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB103">
         <v>8000</v>
@@ -9975,7 +9975,7 @@
         <v>109</v>
       </c>
       <c r="AA104">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB104">
         <v>8000</v>
@@ -10064,7 +10064,7 @@
         <v>109</v>
       </c>
       <c r="AA105">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB105">
         <v>8000</v>
@@ -10509,7 +10509,7 @@
         <v>109</v>
       </c>
       <c r="AA110">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB110">
         <v>8000</v>
@@ -10598,7 +10598,7 @@
         <v>109</v>
       </c>
       <c r="AA111">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB111">
         <v>8000</v>
@@ -10687,7 +10687,7 @@
         <v>109</v>
       </c>
       <c r="AA112">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB112">
         <v>8000</v>
@@ -10776,7 +10776,7 @@
         <v>109</v>
       </c>
       <c r="AA113">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB113">
         <v>8000</v>
@@ -10865,7 +10865,7 @@
         <v>109</v>
       </c>
       <c r="AA114">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB114">
         <v>8000</v>
@@ -10954,7 +10954,7 @@
         <v>109</v>
       </c>
       <c r="AA115">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB115">
         <v>8000</v>
@@ -11043,7 +11043,7 @@
         <v>109</v>
       </c>
       <c r="AA116">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB116">
         <v>8000</v>
@@ -11132,7 +11132,7 @@
         <v>109</v>
       </c>
       <c r="AA117">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB117">
         <v>8000</v>
@@ -11221,7 +11221,7 @@
         <v>109</v>
       </c>
       <c r="AA118">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB118">
         <v>8000</v>
@@ -11310,7 +11310,7 @@
         <v>109</v>
       </c>
       <c r="AA119">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB119">
         <v>8000</v>
@@ -11399,7 +11399,7 @@
         <v>109</v>
       </c>
       <c r="AA120">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB120">
         <v>8000</v>
@@ -11488,7 +11488,7 @@
         <v>109</v>
       </c>
       <c r="AA121">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB121">
         <v>8000</v>
@@ -13357,7 +13357,7 @@
         <v>109</v>
       </c>
       <c r="AA142">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB142">
         <v>8000</v>
@@ -13446,7 +13446,7 @@
         <v>109</v>
       </c>
       <c r="AA143">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB143">
         <v>8000</v>
@@ -13535,7 +13535,7 @@
         <v>109</v>
       </c>
       <c r="AA144">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB144">
         <v>8000</v>
@@ -13624,7 +13624,7 @@
         <v>109</v>
       </c>
       <c r="AA145">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB145">
         <v>8000</v>
@@ -13713,7 +13713,7 @@
         <v>109</v>
       </c>
       <c r="AA146">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB146">
         <v>8000</v>
@@ -13802,7 +13802,7 @@
         <v>109</v>
       </c>
       <c r="AA147">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB147">
         <v>8000</v>
@@ -13891,7 +13891,7 @@
         <v>109</v>
       </c>
       <c r="AA148">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB148">
         <v>8000</v>
@@ -13980,7 +13980,7 @@
         <v>109</v>
       </c>
       <c r="AA149">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB149">
         <v>8000</v>
@@ -14069,7 +14069,7 @@
         <v>109</v>
       </c>
       <c r="AA150">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB150">
         <v>8000</v>
@@ -14158,7 +14158,7 @@
         <v>109</v>
       </c>
       <c r="AA151">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB151">
         <v>8000</v>
@@ -14247,7 +14247,7 @@
         <v>109</v>
       </c>
       <c r="AA152">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB152">
         <v>8000</v>
@@ -14336,7 +14336,7 @@
         <v>109</v>
       </c>
       <c r="AA153">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB153">
         <v>8000</v>
@@ -14425,7 +14425,7 @@
         <v>109</v>
       </c>
       <c r="AA154">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB154">
         <v>8000</v>
@@ -14514,7 +14514,7 @@
         <v>109</v>
       </c>
       <c r="AA155">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB155">
         <v>8000</v>
@@ -14603,7 +14603,7 @@
         <v>109</v>
       </c>
       <c r="AA156">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB156">
         <v>8000</v>
@@ -14692,7 +14692,7 @@
         <v>109</v>
       </c>
       <c r="AA157">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB157">
         <v>8000</v>
@@ -14781,7 +14781,7 @@
         <v>109</v>
       </c>
       <c r="AA158">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB158">
         <v>8000</v>
@@ -14870,7 +14870,7 @@
         <v>109</v>
       </c>
       <c r="AA159">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB159">
         <v>8000</v>
@@ -14959,7 +14959,7 @@
         <v>109</v>
       </c>
       <c r="AA160">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB160">
         <v>8000</v>
@@ -15048,7 +15048,7 @@
         <v>109</v>
       </c>
       <c r="AA161">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB161">
         <v>8000</v>
@@ -15137,7 +15137,7 @@
         <v>109</v>
       </c>
       <c r="AA162">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AB162">
         <v>8000</v>
@@ -15226,7 +15226,7 @@
         <v>109</v>
       </c>
       <c r="AA163">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AB163">
         <v>8000</v>
@@ -15315,7 +15315,7 @@
         <v>109</v>
       </c>
       <c r="AA164">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AB164">
         <v>8000</v>
@@ -15404,7 +15404,7 @@
         <v>109</v>
       </c>
       <c r="AA165">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AB165">
         <v>8000</v>
@@ -15493,7 +15493,7 @@
         <v>109</v>
       </c>
       <c r="AA166">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AB166">
         <v>8000</v>
@@ -15582,7 +15582,7 @@
         <v>109</v>
       </c>
       <c r="AA167">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AB167">
         <v>8000</v>
@@ -15671,7 +15671,7 @@
         <v>109</v>
       </c>
       <c r="AA168">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AB168">
         <v>8000</v>
@@ -15760,7 +15760,7 @@
         <v>109</v>
       </c>
       <c r="AA169">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AB169">
         <v>8000</v>
@@ -16561,7 +16561,7 @@
         <v>109</v>
       </c>
       <c r="AA178">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB178">
         <v>8000</v>
@@ -16650,7 +16650,7 @@
         <v>109</v>
       </c>
       <c r="AA179">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB179">
         <v>8000</v>
@@ -16739,7 +16739,7 @@
         <v>109</v>
       </c>
       <c r="AA180">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB180">
         <v>8000</v>
@@ -16828,7 +16828,7 @@
         <v>109</v>
       </c>
       <c r="AA181">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB181">
         <v>8000</v>
@@ -16917,7 +16917,7 @@
         <v>109</v>
       </c>
       <c r="AA182">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB182">
         <v>8000</v>
@@ -17006,7 +17006,7 @@
         <v>109</v>
       </c>
       <c r="AA183">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB183">
         <v>8000</v>
@@ -17095,7 +17095,7 @@
         <v>109</v>
       </c>
       <c r="AA184">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB184">
         <v>8000</v>
@@ -17184,7 +17184,7 @@
         <v>109</v>
       </c>
       <c r="AA185">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB185">
         <v>8000</v>
